--- a/data_lake/industry/CFM/eMCP.xlsx
+++ b/data_lake/industry/CFM/eMCP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5D26E1-FFE9-49E0-A0EB-76CB30C4A459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2519194E-74B6-44E0-A414-011B06599281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -69,29 +69,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -100,9 +100,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,36 +129,36 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -437,19 +442,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -495,7 +500,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -518,7 +523,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -541,7 +546,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -564,7 +569,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -587,7 +592,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -610,7 +615,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -633,7 +638,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -656,7 +661,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -679,7 +684,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -702,7 +707,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -725,7 +730,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -748,7 +753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -771,7 +776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -794,7 +799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -817,7 +822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -840,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -863,7 +868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -886,7 +891,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -909,7 +914,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -932,7 +937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -955,7 +960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -978,7 +983,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1001,7 +1006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1024,7 +1029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1047,7 +1052,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1070,7 +1075,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1093,7 +1098,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1116,7 +1121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1139,7 +1144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1162,7 +1167,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1185,7 +1190,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1208,7 +1213,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1231,7 +1236,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1254,7 +1259,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1277,7 +1282,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1300,7 +1305,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1323,7 +1328,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1346,7 +1351,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1369,7 +1374,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1392,7 +1397,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1415,7 +1420,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1438,7 +1443,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1461,7 +1466,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1484,7 +1489,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1507,7 +1512,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1530,7 +1535,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1550,6 +1555,121 @@
         <v>84.7</v>
       </c>
       <c r="G48" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>82</v>
+      </c>
+      <c r="F49" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G49" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>82</v>
+      </c>
+      <c r="F50" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G50" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>82</v>
+      </c>
+      <c r="F51" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G51" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>82</v>
+      </c>
+      <c r="F52" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G52" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>82</v>
+      </c>
+      <c r="F53" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G53" s="9">
         <v>83</v>
       </c>
     </row>
@@ -1562,19 +1682,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6D90D4-0805-4F1F-B873-D654865F68EF}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1597,7 +1717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1620,7 +1740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1643,7 +1763,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1666,7 +1786,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1689,7 +1809,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1712,7 +1832,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1735,7 +1855,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1758,7 +1878,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1781,7 +1901,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1804,7 +1924,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1827,7 +1947,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1850,7 +1970,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1873,7 +1993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1896,7 +2016,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1919,7 +2039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1942,7 +2062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1965,7 +2085,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1988,7 +2108,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2011,7 +2131,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2034,7 +2154,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2057,7 +2177,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2080,7 +2200,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2103,7 +2223,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2126,7 +2246,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2149,7 +2269,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2172,7 +2292,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2195,7 +2315,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2218,7 +2338,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2241,7 +2361,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2264,7 +2384,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2287,7 +2407,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2310,7 +2430,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2333,7 +2453,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2356,7 +2476,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2379,7 +2499,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2402,7 +2522,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2425,7 +2545,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2448,7 +2568,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2471,7 +2591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2494,7 +2614,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2517,7 +2637,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2540,7 +2660,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2563,7 +2683,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2586,7 +2706,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2609,7 +2729,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2632,7 +2752,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2655,7 +2775,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2675,6 +2795,121 @@
         <v>90.5</v>
       </c>
       <c r="G48" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333331899</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G49" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333331799</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G50" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333331699</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G51" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.458333333333316</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G52" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.458333333333315</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G53" s="9">
         <v>89</v>
       </c>
     </row>
@@ -2687,20 +2922,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F328918B-C38E-4C53-9F1E-0761925FE522}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="9"/>
-    <col min="6" max="6" width="10.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2723,7 +2958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2746,7 +2981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2769,7 +3004,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2792,7 +3027,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2815,7 +3050,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2838,7 +3073,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2861,7 +3096,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2884,7 +3119,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2907,7 +3142,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2930,7 +3165,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2953,7 +3188,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2976,7 +3211,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2999,7 +3234,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3022,7 +3257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3045,7 +3280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3068,7 +3303,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3091,7 +3326,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3114,7 +3349,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3137,7 +3372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3160,7 +3395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3183,7 +3418,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3206,7 +3441,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3229,7 +3464,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3252,7 +3487,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3275,7 +3510,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3298,7 +3533,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3321,7 +3556,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3344,7 +3579,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3367,7 +3602,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3390,7 +3625,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3413,7 +3648,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3436,7 +3671,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3459,7 +3694,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3482,7 +3717,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3505,7 +3740,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3528,7 +3763,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3551,7 +3786,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3574,7 +3809,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3597,7 +3832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3620,7 +3855,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3643,7 +3878,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3666,7 +3901,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3689,7 +3924,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3712,7 +3947,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3735,7 +3970,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3758,7 +3993,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3781,7 +4016,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3801,6 +4036,121 @@
         <v>109</v>
       </c>
       <c r="G48" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333331899</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>109</v>
+      </c>
+      <c r="G49" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333331799</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>109</v>
+      </c>
+      <c r="G50" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333331699</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>109</v>
+      </c>
+      <c r="G51" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.458333333333316</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>109</v>
+      </c>
+      <c r="G52" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.458333333333315</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>109</v>
+      </c>
+      <c r="G53" s="9">
         <v>107</v>
       </c>
     </row>
